--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CAJA RURAL RDL.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CAJA RURAL RDL.xlsx
@@ -565,13 +565,13 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>85.0737</v>
+        <v>53.7743</v>
       </c>
       <c r="E2" t="n">
-        <v>47.0224</v>
+        <v>30.3646</v>
       </c>
       <c r="F2" t="n">
-        <v>38.0514</v>
+        <v>23.4098</v>
       </c>
       <c r="G2" t="n">
         <v>29.3515</v>
@@ -610,13 +610,13 @@
         <v>48.3743</v>
       </c>
       <c r="S2" t="n">
-        <v>45.4662</v>
+        <v>14.167</v>
       </c>
       <c r="T2" t="n">
-        <v>22.5795</v>
+        <v>5.9216</v>
       </c>
       <c r="U2" t="n">
-        <v>22.8864</v>
+        <v>8.2448</v>
       </c>
       <c r="V2" t="n">
         <v>27.6868</v>
@@ -643,13 +643,13 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>36.521</v>
+        <v>50.5411</v>
       </c>
       <c r="E3" t="n">
-        <v>34.3407</v>
+        <v>41.5537</v>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>8.987500000000001</v>
       </c>
       <c r="G3" t="n">
         <v>31.0946</v>
@@ -688,13 +688,13 @@
         <v>53.8582</v>
       </c>
       <c r="S3" t="n">
-        <v>-24.9604</v>
+        <v>-10.9401</v>
       </c>
       <c r="T3" t="n">
-        <v>-14.4254</v>
+        <v>-7.2123</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.5351</v>
+        <v>-3.7274</v>
       </c>
       <c r="V3" t="n">
         <v>15.3063</v>
@@ -721,13 +721,13 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>32.5622</v>
+        <v>33.4158</v>
       </c>
       <c r="E4" t="n">
-        <v>35.6577</v>
+        <v>37.4101</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.095300000000001</v>
+        <v>-3.9946</v>
       </c>
       <c r="G4" t="n">
         <v>19.7577</v>
@@ -766,13 +766,13 @@
         <v>53.4663</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.06969999999999987</v>
+        <v>0.7834999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.2969</v>
+        <v>-4.5441</v>
       </c>
       <c r="U4" t="n">
-        <v>6.2267</v>
+        <v>5.327199999999999</v>
       </c>
       <c r="V4" t="n">
         <v>14.4416</v>
@@ -799,13 +799,13 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3114</v>
+        <v>2.7115</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1868</v>
+        <v>0.5626999999999995</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1248</v>
+        <v>2.1488</v>
       </c>
       <c r="G5" t="n">
         <v>4.3771</v>
@@ -844,13 +844,13 @@
         <v>7.8338</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5736</v>
+        <v>2.9737</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9143</v>
+        <v>1.2904</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6593</v>
+        <v>1.6834</v>
       </c>
       <c r="V5" t="n">
         <v>2.2155</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. PRIETO GONZALEZ</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1923</v>
+        <v>1.9254</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1174</v>
+        <v>21.5436</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-19.6184</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0058</v>
+        <v>16.1482</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3191</v>
+        <v>-1.595999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3133</v>
+        <v>17.7443</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0608</v>
+        <v>42.3366</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0204</v>
+        <v>13.8282</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404</v>
+        <v>28.5085</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0667</v>
+        <v>-26.1888</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3396</v>
+        <v>-15.4239</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2729</v>
+        <v>-10.7644</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>1.1752</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-33.8813</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1958</v>
+        <v>35.0565</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1069</v>
+        <v>-8.0717</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1782</v>
+        <v>-3.2075</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0713</v>
+        <v>-4.8641</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>-7.3268</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>16.2967</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>-23.6234</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5543000000000005</v>
+        <v>0.5725999999999998</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3599</v>
+        <v>3.5217</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9143</v>
+        <v>-2.9494</v>
       </c>
       <c r="G7" t="n">
         <v>1.2144</v>
@@ -1000,13 +1000,13 @@
         <v>4.896</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5266</v>
+        <v>-0.3997</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5205</v>
+        <v>-0.3586999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.006</v>
+        <v>-0.04089999999999998</v>
       </c>
       <c r="V7" t="n">
         <v>-2.9841</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BLANCO RAMOS</t>
+          <t>D. PRIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.775600000000001</v>
+        <v>-0.0259</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6206</v>
+        <v>-0.058</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.155</v>
+        <v>0.032</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6401</v>
+        <v>-0.0058</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4073</v>
+        <v>-0.3191</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2328</v>
+        <v>0.3133</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2432</v>
+        <v>0.0608</v>
       </c>
       <c r="K8" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.0667</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.3396</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>-1.2432</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.3969</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.4073</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.01040000000000002</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.3917</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.9792</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8549</v>
+        <v>0.0594</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3982</v>
+        <v>-0.1188</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4567</v>
+        <v>0.1782</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.889</v>
+        <v>-0.2754</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.889</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.882500000000003</v>
+        <v>-1.398800000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>18.3914</v>
+        <v>2.017899999999998</v>
       </c>
       <c r="F9" t="n">
-        <v>-24.2735</v>
+        <v>-3.4166</v>
       </c>
       <c r="G9" t="n">
-        <v>16.1482</v>
+        <v>-10.6354</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.595999999999999</v>
+        <v>-1.870800000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>17.7443</v>
+        <v>-8.764900000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>42.3366</v>
+        <v>18.4364</v>
       </c>
       <c r="K9" t="n">
-        <v>13.8282</v>
+        <v>16.7302</v>
       </c>
       <c r="L9" t="n">
-        <v>28.5085</v>
+        <v>1.7059</v>
       </c>
       <c r="M9" t="n">
-        <v>-26.1888</v>
+        <v>-29.0715</v>
       </c>
       <c r="N9" t="n">
-        <v>-15.4239</v>
+        <v>-18.6009</v>
       </c>
       <c r="O9" t="n">
-        <v>-10.7644</v>
+        <v>-10.4708</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1752</v>
+        <v>4.896</v>
       </c>
       <c r="Q9" t="n">
-        <v>-33.8813</v>
+        <v>-39.1692</v>
       </c>
       <c r="R9" t="n">
-        <v>35.0565</v>
+        <v>44.0656</v>
       </c>
       <c r="S9" t="n">
-        <v>-15.8788</v>
+        <v>-7.8255</v>
       </c>
       <c r="T9" t="n">
-        <v>-6.359500000000001</v>
+        <v>-4.4817</v>
       </c>
       <c r="U9" t="n">
-        <v>-9.519299999999999</v>
+        <v>-3.3439</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.3268</v>
+        <v>12.1658</v>
       </c>
       <c r="W9" t="n">
-        <v>16.2967</v>
+        <v>27.2335</v>
       </c>
       <c r="X9" t="n">
-        <v>-23.6234</v>
+        <v>-15.0675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FERNÁNDEZ DEL RÍO</t>
+          <t>D. BLANCO RAMOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3472</v>
+        <v>-4.1644</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7016</v>
+        <v>-2.416</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6455</v>
+        <v>-1.7484</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4466</v>
+        <v>-1.6401</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.543</v>
+        <v>-0.4073</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0965</v>
+        <v>-1.2328</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5012000000000002</v>
+        <v>-1.2432</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7401</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2414</v>
+        <v>-1.2432</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9478</v>
+        <v>-0.3969</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.8029</v>
+        <v>-0.4073</v>
       </c>
       <c r="O10" t="n">
-        <v>0.855</v>
+        <v>0.01040000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1959</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9376</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7417</v>
+        <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.642</v>
+        <v>-0.2437</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5992</v>
+        <v>-0.1935</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0427</v>
+        <v>-0.05010000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0629</v>
+        <v>-1.889</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3971</v>
+        <v>-1.889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PEREZ MARTIN</t>
+          <t>J. FERNÁNDEZ DEL RÍO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.127600000000001</v>
+        <v>-4.750500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.508000000000001</v>
+        <v>-3.8828</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.619899999999999</v>
+        <v>-0.8676000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>8.344799999999999</v>
+        <v>-2.4466</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1429</v>
+        <v>-4.543</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2018</v>
+        <v>2.0965</v>
       </c>
       <c r="J11" t="n">
-        <v>29.9845</v>
+        <v>0.5012000000000002</v>
       </c>
       <c r="K11" t="n">
-        <v>15.8972</v>
+        <v>-0.7401</v>
       </c>
       <c r="L11" t="n">
-        <v>14.0871</v>
+        <v>1.2414</v>
       </c>
       <c r="M11" t="n">
-        <v>-21.6398</v>
+        <v>-2.9478</v>
       </c>
       <c r="N11" t="n">
-        <v>-12.7542</v>
+        <v>-3.8029</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.8855</v>
+        <v>0.855</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.462999999999999</v>
+        <v>-0.1959</v>
       </c>
       <c r="Q11" t="n">
-        <v>-42.499</v>
+        <v>-2.9376</v>
       </c>
       <c r="R11" t="n">
-        <v>36.0358</v>
+        <v>2.7417</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.9798</v>
+        <v>-1.0451</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7126000000000001</v>
+        <v>-0.7805</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.2675</v>
+        <v>-0.2645</v>
       </c>
       <c r="V11" t="n">
-        <v>-6.030099999999999</v>
+        <v>-1.0629</v>
       </c>
       <c r="W11" t="n">
-        <v>10.7192</v>
+        <v>-0.6659</v>
       </c>
       <c r="X11" t="n">
-        <v>-16.7492</v>
+        <v>-0.3971</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>R. PEREZ MARTIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.8016</v>
+        <v>-7.837999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.719300000000002</v>
+        <v>-2.7326</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.0825</v>
+        <v>-5.1048</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.6354</v>
+        <v>8.344799999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.870800000000001</v>
+        <v>3.1429</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.764900000000001</v>
+        <v>5.2018</v>
       </c>
       <c r="J12" t="n">
-        <v>18.4364</v>
+        <v>29.9845</v>
       </c>
       <c r="K12" t="n">
-        <v>16.7302</v>
+        <v>15.8972</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7059</v>
+        <v>14.0871</v>
       </c>
       <c r="M12" t="n">
-        <v>-29.0715</v>
+        <v>-21.6398</v>
       </c>
       <c r="N12" t="n">
-        <v>-18.6009</v>
+        <v>-12.7542</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.4708</v>
+        <v>-8.8855</v>
       </c>
       <c r="P12" t="n">
-        <v>4.896</v>
+        <v>-6.462999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-39.1692</v>
+        <v>-42.499</v>
       </c>
       <c r="R12" t="n">
-        <v>44.0656</v>
+        <v>36.0358</v>
       </c>
       <c r="S12" t="n">
-        <v>-20.2285</v>
+        <v>-3.6899</v>
       </c>
       <c r="T12" t="n">
-        <v>-10.219</v>
+        <v>-0.9370000000000003</v>
       </c>
       <c r="U12" t="n">
-        <v>-10.0093</v>
+        <v>-2.7528</v>
       </c>
       <c r="V12" t="n">
-        <v>12.1658</v>
+        <v>-6.030099999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>27.2335</v>
+        <v>10.7192</v>
       </c>
       <c r="X12" t="n">
-        <v>-15.0675</v>
+        <v>-16.7492</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.6402</v>
+        <v>-12.4662</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.427499999999999</v>
+        <v>-1.6517</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.213</v>
+        <v>-10.8147</v>
       </c>
       <c r="G13" t="n">
         <v>-2.795600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>18.8009</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.559600000000001</v>
+        <v>-3.3854</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1733</v>
+        <v>-1.3976</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.3866</v>
+        <v>-1.988</v>
       </c>
       <c r="V13" t="n">
         <v>-18.8193</v>
@@ -1501,13 +1501,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.2276</v>
+        <v>-18.4901</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.7994</v>
+        <v>-19.9877</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5718000000000001</v>
+        <v>1.4975</v>
       </c>
       <c r="G14" t="n">
         <v>0.0270999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>19.193</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.331100000000001</v>
+        <v>-7.5933</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.0852</v>
+        <v>-4.2735</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.2455</v>
+        <v>-3.32</v>
       </c>
       <c r="V14" t="n">
         <v>-8.769600000000001</v>
@@ -1579,13 +1579,13 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>-20.9294</v>
+        <v>-23.0579</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.6607</v>
+        <v>-16.6908</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.2689</v>
+        <v>-6.367599999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-13.4365</v>
@@ -1624,13 +1624,13 @@
         <v>11.163</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6666</v>
+        <v>1.5378</v>
       </c>
       <c r="T15" t="n">
-        <v>4.6738</v>
+        <v>2.6436</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0072</v>
+        <v>-1.1056</v>
       </c>
       <c r="V15" t="n">
         <v>-2.5423</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-37.185</v>
+        <v>-25.3978</v>
       </c>
       <c r="E16" t="n">
-        <v>-27.4653</v>
+        <v>-22.7617</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.7195</v>
+        <v>-2.6365</v>
       </c>
       <c r="G16" t="n">
         <v>-15.6053</v>
@@ -1702,13 +1702,13 @@
         <v>49.5495</v>
       </c>
       <c r="S16" t="n">
-        <v>-20.4297</v>
+        <v>-8.6426</v>
       </c>
       <c r="T16" t="n">
-        <v>-10.1201</v>
+        <v>-5.4163</v>
       </c>
       <c r="U16" t="n">
-        <v>-10.3098</v>
+        <v>-3.2264</v>
       </c>
       <c r="V16" t="n">
         <v>0.6130000000000002</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>24.80500000000002</v>
+        <v>45.3511</v>
       </c>
       <c r="E17" t="n">
-        <v>61.93909999999997</v>
+        <v>66.79299999999996</v>
       </c>
       <c r="F17" t="n">
-        <v>-37.13430000000001</v>
+        <v>-21.443</v>
       </c>
       <c r="G17" t="n">
         <v>63.75009999999999</v>
@@ -1768,28 +1768,28 @@
         <v>-159.2193</v>
       </c>
       <c r="O17" t="n">
-        <v>-90.69309999999999</v>
+        <v>-90.6931</v>
       </c>
       <c r="P17" t="n">
-        <v>-8.813800000000002</v>
+        <v>-8.813800000000001</v>
       </c>
       <c r="Q17" t="n">
         <v>-394.6317999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>385.8179</v>
+        <v>385.8179000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-52.8616</v>
+        <v>-32.3156</v>
       </c>
       <c r="T17" t="n">
-        <v>-27.9205</v>
+        <v>-23.06590000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-24.942</v>
+        <v>-9.2501</v>
       </c>
       <c r="V17" t="n">
-        <v>22.7295</v>
+        <v>22.72949999999999</v>
       </c>
       <c r="W17" t="n">
         <v>170.8358</v>
